--- a/shipClassTests/testResults/system_example.xlsx
+++ b/shipClassTests/testResults/system_example.xlsx
@@ -8,13 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="TestSystem" sheetId="1" r:id="rId1"/>
+    <sheet name="Component_1" sheetId="2" r:id="rId2"/>
+    <sheet name="Component_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Component_3" sheetId="4" r:id="rId4"/>
+    <sheet name="Component_4" sheetId="5" r:id="rId5"/>
+    <sheet name="Component_5" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
   <si>
     <t>Time Step</t>
   </si>
@@ -35,6 +40,9 @@
   </si>
   <si>
     <t>Component_5 Truth State</t>
+  </si>
+  <si>
+    <t>Comp Truth State</t>
   </si>
 </sst>
 </file>
@@ -66,42 +74,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -122,13 +100,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -518,13 +496,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -533,7 +511,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -541,13 +519,13 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -556,7 +534,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -567,7 +545,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -579,7 +557,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -590,7 +568,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -602,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -610,22 +588,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -633,22 +611,22 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -659,19 +637,19 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -679,22 +657,22 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -705,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -717,7 +695,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -728,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -740,7 +718,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -751,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -763,7 +741,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -771,22 +749,22 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -797,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -806,10 +784,10 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -817,10 +795,10 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -832,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -840,10 +818,10 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -855,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -863,10 +841,10 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -878,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -886,10 +864,10 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -901,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -909,10 +887,10 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -924,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -932,22 +910,22 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -955,7 +933,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -964,13 +942,13 @@
         <v>2</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -984,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1007,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1030,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1053,16 +1031,16 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1108,4 +1086,1149 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="7" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="7" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="7" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="7" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="7" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/shipClassTests/testResults/system_example.xlsx
+++ b/shipClassTests/testResults/system_example.xlsx
@@ -496,7 +496,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -505,13 +505,13 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -519,7 +519,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -528,13 +528,13 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -542,7 +542,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -551,13 +551,13 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -568,7 +568,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -580,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -588,22 +588,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -617,16 +617,16 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -634,22 +634,22 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -657,22 +657,22 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -680,22 +680,22 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -703,22 +703,22 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -726,22 +726,22 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -749,22 +749,22 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -772,22 +772,22 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -798,19 +798,19 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -821,19 +821,19 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -844,19 +844,19 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -867,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -890,19 +890,19 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -916,16 +916,16 @@
         <v>2</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -936,19 +936,19 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -959,19 +959,19 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -982,19 +982,19 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1005,19 +1005,19 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1157,7 +1157,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1221,7 +1221,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1229,7 +1229,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1237,7 +1237,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1245,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1253,7 +1253,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1261,7 +1261,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1277,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1285,7 +1285,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1293,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1301,7 +1301,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1309,7 +1309,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +1386,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1394,7 +1394,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1402,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1410,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1418,7 +1418,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1426,7 +1426,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1434,7 +1434,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1442,7 +1442,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1450,7 +1450,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1458,7 +1458,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1466,7 +1466,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1474,7 +1474,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1482,7 +1482,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1490,7 +1490,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1498,7 +1498,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1506,7 +1506,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1514,7 +1514,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1522,7 +1522,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1530,7 +1530,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1538,7 +1538,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1583,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1671,7 +1671,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1679,7 +1679,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1687,7 +1687,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1695,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1703,7 +1703,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1711,7 +1711,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1719,7 +1719,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1844,7 +1844,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1916,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1924,7 +1924,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1932,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1940,7 +1940,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1948,7 +1948,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1956,7 +1956,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1964,7 +1964,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1972,7 +1972,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1980,7 +1980,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1988,7 +1988,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/shipClassTests/testResults/system_example.xlsx
+++ b/shipClassTests/testResults/system_example.xlsx
@@ -479,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -496,16 +496,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -519,16 +519,16 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -542,16 +542,16 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -588,10 +588,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -611,10 +611,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -634,10 +634,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -657,16 +657,16 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -680,10 +680,10 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -703,10 +703,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -729,13 +729,13 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -752,16 +752,16 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="4">
         <v>2</v>
@@ -775,16 +775,16 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4">
         <v>2</v>
@@ -798,16 +798,16 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4">
         <v>2</v>
@@ -821,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4">
         <v>2</v>
@@ -844,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4">
         <v>2</v>
@@ -867,16 +867,16 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4">
         <v>2</v>
@@ -890,16 +890,16 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="4">
         <v>2</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4">
         <v>2</v>
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4">
         <v>2</v>
@@ -959,16 +959,16 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4">
         <v>2</v>
@@ -982,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="4">
         <v>2</v>
@@ -1005,16 +1005,16 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4">
         <v>2</v>
@@ -1028,13 +1028,13 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1125,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1133,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1141,7 +1141,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1149,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1157,7 +1157,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1165,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1173,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1181,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1189,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1197,7 +1197,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1205,7 +1205,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1213,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1221,7 +1221,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1229,7 +1229,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1237,7 +1237,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1245,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1253,7 +1253,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1261,7 +1261,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1269,7 +1269,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1277,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1285,7 +1285,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1293,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1301,7 +1301,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1309,7 +1309,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1671,7 +1671,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1679,7 +1679,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1687,7 +1687,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1695,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1703,7 +1703,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1711,7 +1711,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1719,7 +1719,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1727,7 +1727,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1735,7 +1735,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1743,7 +1743,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1751,7 +1751,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1759,7 +1759,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1767,7 +1767,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1900,7 +1900,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1908,7 +1908,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1916,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1924,7 +1924,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1932,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1940,7 +1940,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1948,7 +1948,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1956,7 +1956,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1964,7 +1964,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1972,7 +1972,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1980,7 +1980,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1988,7 +1988,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">

--- a/shipClassTests/testResults/system_example.xlsx
+++ b/shipClassTests/testResults/system_example.xlsx
@@ -479,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -496,13 +496,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -511,7 +511,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -519,13 +519,13 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -534,7 +534,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -545,13 +545,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -591,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4">
         <v>2</v>
@@ -614,13 +614,13 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -637,13 +637,13 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -660,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -683,13 +683,13 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -706,13 +706,13 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -729,13 +729,13 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -752,16 +752,16 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4">
         <v>2</v>
@@ -775,16 +775,16 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4">
         <v>2</v>
@@ -798,16 +798,16 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4">
         <v>2</v>
@@ -821,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4">
         <v>2</v>
@@ -844,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4">
         <v>2</v>
@@ -867,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -890,16 +890,16 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4">
         <v>2</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4">
         <v>2</v>
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4">
         <v>2</v>
@@ -959,16 +959,16 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4">
         <v>2</v>
@@ -982,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4">
         <v>2</v>
@@ -1005,16 +1005,16 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4">
         <v>2</v>
@@ -1028,16 +1028,16 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
@@ -1125,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1133,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1141,7 +1141,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1149,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1157,7 +1157,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1165,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1173,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1181,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1189,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1197,7 +1197,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1205,7 +1205,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1213,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1221,7 +1221,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1229,7 +1229,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1237,7 +1237,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1245,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1253,7 +1253,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1261,7 +1261,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1269,7 +1269,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1277,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1285,7 +1285,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1293,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1301,7 +1301,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1309,7 +1309,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1386,7 +1386,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1394,7 +1394,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1402,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1410,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1418,7 +1418,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1426,7 +1426,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1434,7 +1434,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1442,7 +1442,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1450,7 +1450,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1458,7 +1458,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1466,7 +1466,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1474,7 +1474,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1482,7 +1482,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1490,7 +1490,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1498,7 +1498,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1506,7 +1506,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1514,7 +1514,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1522,7 +1522,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1530,7 +1530,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1538,7 +1538,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1599,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1671,7 +1671,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1679,7 +1679,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1687,7 +1687,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1695,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1703,7 +1703,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1711,7 +1711,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1719,7 +1719,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1727,7 +1727,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1735,7 +1735,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1743,7 +1743,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1751,7 +1751,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1759,7 +1759,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1767,7 +1767,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1844,7 +1844,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1900,7 +1900,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1908,7 +1908,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1916,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1924,7 +1924,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1932,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1940,7 +1940,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1948,7 +1948,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1956,7 +1956,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1964,7 +1964,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1972,7 +1972,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1980,7 +1980,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1988,7 +1988,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1996,7 +1996,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2041,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/shipClassTests/testResults/system_example.xlsx
+++ b/shipClassTests/testResults/system_example.xlsx
@@ -403,7 +403,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -411,7 +411,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -419,7 +419,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -427,7 +427,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -435,7 +435,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -443,7 +443,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -621,7 +621,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -717,7 +717,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -725,7 +725,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -733,7 +733,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -741,7 +741,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -749,7 +749,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -757,7 +757,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -765,7 +765,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -781,7 +781,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -789,7 +789,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -797,7 +797,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -805,7 +805,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -813,7 +813,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -871,7 +871,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -879,7 +879,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -967,7 +967,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -975,7 +975,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -983,7 +983,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -991,7 +991,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -999,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1007,7 +1007,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1015,7 +1015,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1081,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1089,7 +1089,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1097,7 +1097,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1129,7 +1129,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1137,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1153,7 +1153,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1161,7 +1161,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1169,7 +1169,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1177,7 +1177,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1185,7 +1185,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1193,7 +1193,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1209,7 +1209,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1217,7 +1217,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1225,7 +1225,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1299,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1323,7 +1323,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1339,7 +1339,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1347,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1355,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1363,7 +1363,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1533,7 +1533,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1541,7 +1541,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1549,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1557,7 +1557,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1565,7 +1565,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1581,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1589,7 +1589,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1597,7 +1597,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1605,7 +1605,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1613,7 +1613,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1621,7 +1621,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1629,7 +1629,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1637,7 +1637,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1645,7 +1645,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1653,7 +1653,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1661,7 +1661,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1669,7 +1669,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1677,7 +1677,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1685,7 +1685,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1693,7 +1693,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1701,7 +1701,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1709,7 +1709,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
